--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-10-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6422F5-7F73-42B6-8267-BE0735FB5D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DF4823-E903-4952-80E3-3BF74AD553C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2910" yWindow="1215" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28410" yWindow="1785" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -679,9 +679,6 @@
     <t>£1074.37</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulation-online.com/product/celotex-thermaclass-cavity-wall-21-115mm/</t>
-  </si>
-  <si>
     <t>£1108.13</t>
   </si>
   <si>
@@ -1211,6 +1208,9 @@
   </si>
   <si>
     <t>£61.80</t>
+  </si>
+  <si>
+    <t>£1195.55</t>
   </si>
 </sst>
 </file>
@@ -1654,7 +1654,7 @@
         <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G2" t="s">
         <v>107</v>
@@ -1675,16 +1675,16 @@
         <v>105</v>
       </c>
       <c r="M2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O2" t="s">
         <v>76</v>
       </c>
       <c r="P2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q2" t="s">
         <v>105</v>
@@ -1710,7 +1710,7 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G3" t="s">
         <v>108</v>
@@ -1731,22 +1731,22 @@
         <v>106</v>
       </c>
       <c r="M3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P3" t="s">
         <v>77</v>
       </c>
       <c r="Q3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1766,7 +1766,7 @@
         <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G4" t="s">
         <v>109</v>
@@ -1778,7 +1778,7 @@
         <v>155</v>
       </c>
       <c r="J4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K4" t="s">
         <v>196</v>
@@ -1787,22 +1787,22 @@
         <v>106</v>
       </c>
       <c r="M4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1822,7 +1822,7 @@
         <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G5" t="s">
         <v>110</v>
@@ -1843,22 +1843,22 @@
         <v>106</v>
       </c>
       <c r="M5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P5" t="s">
         <v>79</v>
       </c>
       <c r="Q5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1878,7 +1878,7 @@
         <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G6" t="s">
         <v>111</v>
@@ -1890,7 +1890,7 @@
         <v>157</v>
       </c>
       <c r="J6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K6" t="s">
         <v>198</v>
@@ -1899,22 +1899,22 @@
         <v>106</v>
       </c>
       <c r="M6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="R6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1934,7 +1934,7 @@
         <v>81</v>
       </c>
       <c r="F7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G7" t="s">
         <v>112</v>
@@ -1946,7 +1946,7 @@
         <v>158</v>
       </c>
       <c r="J7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K7" t="s">
         <v>199</v>
@@ -1955,22 +1955,22 @@
         <v>106</v>
       </c>
       <c r="M7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1990,7 +1990,7 @@
         <v>82</v>
       </c>
       <c r="F8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G8" t="s">
         <v>113</v>
@@ -2002,7 +2002,7 @@
         <v>159</v>
       </c>
       <c r="J8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K8" t="s">
         <v>200</v>
@@ -2011,22 +2011,22 @@
         <v>106</v>
       </c>
       <c r="M8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P8" t="s">
         <v>82</v>
       </c>
       <c r="Q8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="R8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -2046,7 +2046,7 @@
         <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G9" t="s">
         <v>114</v>
@@ -2058,7 +2058,7 @@
         <v>160</v>
       </c>
       <c r="J9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K9" t="s">
         <v>201</v>
@@ -2067,22 +2067,22 @@
         <v>106</v>
       </c>
       <c r="M9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P9" t="s">
         <v>83</v>
       </c>
       <c r="Q9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -2102,7 +2102,7 @@
         <v>84</v>
       </c>
       <c r="F10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G10" t="s">
         <v>115</v>
@@ -2123,22 +2123,22 @@
         <v>106</v>
       </c>
       <c r="M10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -2158,7 +2158,7 @@
         <v>85</v>
       </c>
       <c r="F11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G11" t="s">
         <v>116</v>
@@ -2179,22 +2179,22 @@
         <v>106</v>
       </c>
       <c r="M11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -2214,7 +2214,7 @@
         <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G12" t="s">
         <v>117</v>
@@ -2235,22 +2235,22 @@
         <v>106</v>
       </c>
       <c r="M12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -2270,7 +2270,7 @@
         <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G13" t="s">
         <v>118</v>
@@ -2291,22 +2291,22 @@
         <v>105</v>
       </c>
       <c r="M13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O13" t="s">
         <v>87</v>
       </c>
       <c r="P13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -2326,7 +2326,7 @@
         <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G14" t="s">
         <v>119</v>
@@ -2347,22 +2347,22 @@
         <v>106</v>
       </c>
       <c r="M14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -2382,7 +2382,7 @@
         <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G15" t="s">
         <v>120</v>
@@ -2403,22 +2403,22 @@
         <v>106</v>
       </c>
       <c r="M15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P15" t="s">
         <v>89</v>
       </c>
       <c r="Q15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -2438,7 +2438,7 @@
         <v>105</v>
       </c>
       <c r="F16" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
@@ -2450,7 +2450,7 @@
         <v>167</v>
       </c>
       <c r="J16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K16" t="s">
         <v>208</v>
@@ -2459,19 +2459,19 @@
         <v>106</v>
       </c>
       <c r="M16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P16" t="s">
         <v>90</v>
       </c>
       <c r="Q16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R16" t="s">
         <v>105</v>
@@ -2494,7 +2494,7 @@
         <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G17" t="s">
         <v>122</v>
@@ -2515,22 +2515,22 @@
         <v>106</v>
       </c>
       <c r="M17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="R17" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -2550,7 +2550,7 @@
         <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G18" t="s">
         <v>105</v>
@@ -2571,19 +2571,19 @@
         <v>105</v>
       </c>
       <c r="M18" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P18" t="s">
         <v>92</v>
       </c>
       <c r="Q18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="R18" t="s">
         <v>105</v>
@@ -2618,7 +2618,7 @@
         <v>170</v>
       </c>
       <c r="J19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K19" t="s">
         <v>211</v>
@@ -2627,22 +2627,22 @@
         <v>105</v>
       </c>
       <c r="M19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P19" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="R19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2662,7 +2662,7 @@
         <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G20" t="s">
         <v>124</v>
@@ -2683,22 +2683,22 @@
         <v>106</v>
       </c>
       <c r="M20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P20" t="s">
         <v>94</v>
       </c>
       <c r="Q20" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="R20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2718,7 +2718,7 @@
         <v>95</v>
       </c>
       <c r="F21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G21" t="s">
         <v>95</v>
@@ -2739,22 +2739,22 @@
         <v>106</v>
       </c>
       <c r="M21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P21" t="s">
         <v>95</v>
       </c>
       <c r="Q21" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="R21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2774,7 +2774,7 @@
         <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G22" t="s">
         <v>125</v>
@@ -2795,22 +2795,22 @@
         <v>106</v>
       </c>
       <c r="M22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q22" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="R22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2830,7 +2830,7 @@
         <v>97</v>
       </c>
       <c r="F23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G23" t="s">
         <v>126</v>
@@ -2842,7 +2842,7 @@
         <v>173</v>
       </c>
       <c r="J23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K23" t="s">
         <v>215</v>
@@ -2851,22 +2851,22 @@
         <v>106</v>
       </c>
       <c r="M23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s">
         <v>97</v>
       </c>
       <c r="Q23" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2886,7 +2886,7 @@
         <v>98</v>
       </c>
       <c r="F24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G24" t="s">
         <v>105</v>
@@ -2907,10 +2907,10 @@
         <v>106</v>
       </c>
       <c r="M24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O24" t="s">
         <v>98</v>
@@ -2919,10 +2919,10 @@
         <v>98</v>
       </c>
       <c r="Q24" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="R24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2942,7 +2942,7 @@
         <v>99</v>
       </c>
       <c r="F25" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G25" t="s">
         <v>105</v>
@@ -2954,7 +2954,7 @@
         <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K25" t="s">
         <v>216</v>
@@ -2963,10 +2963,10 @@
         <v>106</v>
       </c>
       <c r="M25" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O25" t="s">
         <v>99</v>
@@ -2975,10 +2975,10 @@
         <v>99</v>
       </c>
       <c r="Q25" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="R25" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -3010,7 +3010,7 @@
         <v>105</v>
       </c>
       <c r="J26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K26" t="s">
         <v>105</v>
@@ -3019,10 +3019,10 @@
         <v>105</v>
       </c>
       <c r="M26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N26" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O26" t="s">
         <v>100</v>
@@ -3054,7 +3054,7 @@
         <v>101</v>
       </c>
       <c r="F27" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G27" t="s">
         <v>105</v>
@@ -3075,10 +3075,10 @@
         <v>106</v>
       </c>
       <c r="M27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O27" t="s">
         <v>101</v>
@@ -3087,10 +3087,10 @@
         <v>101</v>
       </c>
       <c r="Q27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="R27" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -3110,7 +3110,7 @@
         <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G28" t="s">
         <v>105</v>
@@ -3131,22 +3131,22 @@
         <v>106</v>
       </c>
       <c r="M28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3166,7 +3166,7 @@
         <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G29" t="s">
         <v>105</v>
@@ -3181,28 +3181,28 @@
         <v>105</v>
       </c>
       <c r="K29" t="s">
-        <v>219</v>
+        <v>396</v>
       </c>
       <c r="L29" t="s">
         <v>106</v>
       </c>
       <c r="M29" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N29" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q29" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="R29" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -3222,7 +3222,7 @@
         <v>104</v>
       </c>
       <c r="F30" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G30" t="s">
         <v>105</v>
@@ -3237,28 +3237,28 @@
         <v>105</v>
       </c>
       <c r="K30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L30" t="s">
         <v>105</v>
       </c>
       <c r="M30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q30" t="s">
         <v>105</v>
       </c>
       <c r="R30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
